--- a/election_results_1951.xlsx
+++ b/election_results_1951.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\Dropbox\UK_GE\New_UK_Map\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\Dropbox\UK_GE\UK_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F65400-6491-4CEC-B9A4-A3B8EE01D5FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90954F2F-D947-4BFB-AF21-9DEA410056B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4802,9 +4802,6 @@
     <t>Jim Griffiths</t>
   </si>
   <si>
-    <t>Denbighshire Denbigh</t>
-  </si>
-  <si>
     <t>denbighshire denbigh</t>
   </si>
   <si>
@@ -5682,6 +5679,9 @@
   </si>
   <si>
     <t>somerset bridgewater</t>
+  </si>
+  <si>
+    <t>Denbigh</t>
   </si>
 </sst>
 </file>
@@ -5717,9 +5717,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -26228,13 +26226,13 @@
       <c r="A442">
         <v>473</v>
       </c>
-      <c r="B442" s="2" t="s">
+      <c r="B442" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C442" t="s">
         <v>1885</v>
       </c>
-      <c r="C442" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="D442" s="2" t="s">
+      <c r="D442" t="s">
         <v>181</v>
       </c>
       <c r="E442" t="s">
@@ -28785,13 +28783,13 @@
       <c r="A498">
         <v>533</v>
       </c>
-      <c r="B498" s="1" t="s">
-        <v>1884</v>
-      </c>
-      <c r="C498" s="1" t="s">
+      <c r="B498" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C498" t="s">
         <v>1513</v>
       </c>
-      <c r="D498" s="1" t="s">
+      <c r="D498" t="s">
         <v>173</v>
       </c>
       <c r="E498" t="s">
@@ -30049,16 +30047,16 @@
         <v>560</v>
       </c>
       <c r="B525" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C525" t="s">
         <v>1593</v>
-      </c>
-      <c r="C525" t="s">
-        <v>1594</v>
       </c>
       <c r="D525" t="s">
         <v>1544</v>
       </c>
       <c r="E525" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="F525" t="s">
         <v>175</v>
@@ -30102,16 +30100,16 @@
         <v>561</v>
       </c>
       <c r="B526" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C526" t="s">
         <v>1596</v>
-      </c>
-      <c r="C526" t="s">
-        <v>1597</v>
       </c>
       <c r="D526" t="s">
         <v>1544</v>
       </c>
       <c r="E526" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="F526" t="s">
         <v>24</v>
@@ -30155,10 +30153,10 @@
         <v>562</v>
       </c>
       <c r="B527" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C527" t="s">
         <v>1599</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1600</v>
       </c>
       <c r="D527" t="s">
         <v>1544</v>
@@ -30196,10 +30194,10 @@
         <v>563</v>
       </c>
       <c r="B528" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C528" t="s">
         <v>1601</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1602</v>
       </c>
       <c r="D528" t="s">
         <v>1544</v>
@@ -30237,16 +30235,16 @@
         <v>564</v>
       </c>
       <c r="B529" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C529" t="s">
         <v>1603</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1604</v>
       </c>
       <c r="D529" t="s">
         <v>1544</v>
       </c>
       <c r="E529" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="F529" t="s">
         <v>24</v>
@@ -30281,16 +30279,16 @@
         <v>565</v>
       </c>
       <c r="B530" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C530" t="s">
         <v>1606</v>
-      </c>
-      <c r="C530" t="s">
-        <v>1607</v>
       </c>
       <c r="D530" t="s">
         <v>1544</v>
       </c>
       <c r="E530" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="F530" t="s">
         <v>25</v>
@@ -30325,16 +30323,16 @@
         <v>566</v>
       </c>
       <c r="B531" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C531" t="s">
         <v>1609</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1610</v>
       </c>
       <c r="D531" t="s">
         <v>1544</v>
       </c>
       <c r="E531" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="F531" t="s">
         <v>24</v>
@@ -30369,16 +30367,16 @@
         <v>567</v>
       </c>
       <c r="B532" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C532" t="s">
         <v>1612</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1613</v>
       </c>
       <c r="D532" t="s">
         <v>1544</v>
       </c>
       <c r="E532" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="F532" t="s">
         <v>24</v>
@@ -30413,16 +30411,16 @@
         <v>568</v>
       </c>
       <c r="B533" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C533" t="s">
         <v>1615</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1616</v>
       </c>
       <c r="D533" t="s">
         <v>1544</v>
       </c>
       <c r="E533" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="F533" t="s">
         <v>24</v>
@@ -30457,16 +30455,16 @@
         <v>569</v>
       </c>
       <c r="B534" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C534" t="s">
         <v>1618</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1619</v>
       </c>
       <c r="D534" t="s">
         <v>1544</v>
       </c>
       <c r="E534" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="F534" t="s">
         <v>24</v>
@@ -30510,16 +30508,16 @@
         <v>570</v>
       </c>
       <c r="B535" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C535" t="s">
         <v>1621</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1622</v>
       </c>
       <c r="D535" t="s">
         <v>1544</v>
       </c>
       <c r="E535" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="F535" t="s">
         <v>24</v>
@@ -30554,10 +30552,10 @@
         <v>571</v>
       </c>
       <c r="B536" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C536" t="s">
         <v>1624</v>
-      </c>
-      <c r="C536" t="s">
-        <v>1625</v>
       </c>
       <c r="D536" t="s">
         <v>1544</v>
@@ -30604,16 +30602,16 @@
         <v>572</v>
       </c>
       <c r="B537" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C537" t="s">
         <v>1626</v>
-      </c>
-      <c r="C537" t="s">
-        <v>1627</v>
       </c>
       <c r="D537" t="s">
         <v>1544</v>
       </c>
       <c r="E537" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="F537" t="s">
         <v>24</v>
@@ -30648,16 +30646,16 @@
         <v>573</v>
       </c>
       <c r="B538" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C538" t="s">
         <v>1629</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1630</v>
       </c>
       <c r="D538" t="s">
         <v>1544</v>
       </c>
       <c r="E538" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="F538" t="s">
         <v>24</v>
@@ -30692,16 +30690,16 @@
         <v>574</v>
       </c>
       <c r="B539" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C539" t="s">
         <v>1632</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1633</v>
       </c>
       <c r="D539" t="s">
         <v>1544</v>
       </c>
       <c r="E539" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="F539" t="s">
         <v>24</v>
@@ -30736,16 +30734,16 @@
         <v>575</v>
       </c>
       <c r="B540" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C540" t="s">
         <v>1635</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1636</v>
       </c>
       <c r="D540" t="s">
         <v>1544</v>
       </c>
       <c r="E540" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="F540" t="s">
         <v>25</v>
@@ -30780,16 +30778,16 @@
         <v>576</v>
       </c>
       <c r="B541" t="s">
+        <v>1637</v>
+      </c>
+      <c r="C541" t="s">
         <v>1638</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1639</v>
       </c>
       <c r="D541" t="s">
         <v>1544</v>
       </c>
       <c r="E541" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="F541" t="s">
         <v>24</v>
@@ -30824,10 +30822,10 @@
         <v>577</v>
       </c>
       <c r="B542" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C542" t="s">
         <v>1641</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1642</v>
       </c>
       <c r="D542" t="s">
         <v>1544</v>
@@ -30865,16 +30863,16 @@
         <v>578</v>
       </c>
       <c r="B543" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C543" t="s">
         <v>1643</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1644</v>
       </c>
       <c r="D543" t="s">
         <v>1544</v>
       </c>
       <c r="E543" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="F543" t="s">
         <v>24</v>
@@ -30918,13 +30916,13 @@
         <v>579</v>
       </c>
       <c r="B544" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C544" t="s">
         <v>1646</v>
       </c>
-      <c r="C544" t="s">
+      <c r="D544" t="s">
         <v>1647</v>
-      </c>
-      <c r="D544" t="s">
-        <v>1648</v>
       </c>
       <c r="E544" t="s">
         <v>136</v>
@@ -30962,13 +30960,13 @@
         <v>580</v>
       </c>
       <c r="B545" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C545" t="s">
         <v>1649</v>
       </c>
-      <c r="C545" t="s">
-        <v>1650</v>
-      </c>
       <c r="D545" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E545" t="s">
         <v>373</v>
@@ -31006,16 +31004,16 @@
         <v>581</v>
       </c>
       <c r="B546" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C546" t="s">
         <v>1651</v>
       </c>
-      <c r="C546" t="s">
+      <c r="D546" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E546" t="s">
         <v>1652</v>
-      </c>
-      <c r="D546" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E546" t="s">
-        <v>1653</v>
       </c>
       <c r="F546" t="s">
         <v>24</v>
@@ -31050,16 +31048,16 @@
         <v>582</v>
       </c>
       <c r="B547" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C547" t="s">
         <v>1654</v>
       </c>
-      <c r="C547" t="s">
+      <c r="D547" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E547" t="s">
         <v>1655</v>
-      </c>
-      <c r="D547" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E547" t="s">
-        <v>1656</v>
       </c>
       <c r="F547" t="s">
         <v>24</v>
@@ -31094,16 +31092,16 @@
         <v>583</v>
       </c>
       <c r="B548" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C548" t="s">
         <v>1657</v>
       </c>
-      <c r="C548" t="s">
+      <c r="D548" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E548" t="s">
         <v>1658</v>
-      </c>
-      <c r="D548" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E548" t="s">
-        <v>1659</v>
       </c>
       <c r="F548" t="s">
         <v>24</v>
@@ -31147,16 +31145,16 @@
         <v>584</v>
       </c>
       <c r="B549" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C549" t="s">
         <v>1660</v>
       </c>
-      <c r="C549" t="s">
+      <c r="D549" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E549" t="s">
         <v>1661</v>
-      </c>
-      <c r="D549" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E549" t="s">
-        <v>1662</v>
       </c>
       <c r="F549" t="s">
         <v>24</v>
@@ -31191,16 +31189,16 @@
         <v>585</v>
       </c>
       <c r="B550" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C550" t="s">
         <v>1663</v>
       </c>
-      <c r="C550" t="s">
+      <c r="D550" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E550" t="s">
         <v>1664</v>
-      </c>
-      <c r="D550" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E550" t="s">
-        <v>1665</v>
       </c>
       <c r="F550" t="s">
         <v>24</v>
@@ -31235,16 +31233,16 @@
         <v>586</v>
       </c>
       <c r="B551" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C551" t="s">
         <v>1666</v>
       </c>
-      <c r="C551" t="s">
+      <c r="D551" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E551" t="s">
         <v>1667</v>
-      </c>
-      <c r="D551" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E551" t="s">
-        <v>1668</v>
       </c>
       <c r="F551" t="s">
         <v>24</v>
@@ -31279,16 +31277,16 @@
         <v>587</v>
       </c>
       <c r="B552" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C552" t="s">
         <v>1669</v>
       </c>
-      <c r="C552" t="s">
+      <c r="D552" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E552" t="s">
         <v>1670</v>
-      </c>
-      <c r="D552" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E552" t="s">
-        <v>1671</v>
       </c>
       <c r="F552" t="s">
         <v>24</v>
@@ -31323,16 +31321,16 @@
         <v>588</v>
       </c>
       <c r="B553" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C553" t="s">
         <v>1672</v>
       </c>
-      <c r="C553" t="s">
+      <c r="D553" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E553" t="s">
         <v>1673</v>
-      </c>
-      <c r="D553" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E553" t="s">
-        <v>1674</v>
       </c>
       <c r="F553" t="s">
         <v>25</v>
@@ -31367,16 +31365,16 @@
         <v>589</v>
       </c>
       <c r="B554" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C554" t="s">
         <v>1675</v>
       </c>
-      <c r="C554" t="s">
+      <c r="D554" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E554" t="s">
         <v>1676</v>
-      </c>
-      <c r="D554" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E554" t="s">
-        <v>1677</v>
       </c>
       <c r="F554" t="s">
         <v>25</v>
@@ -31411,16 +31409,16 @@
         <v>590</v>
       </c>
       <c r="B555" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C555" t="s">
         <v>1678</v>
       </c>
-      <c r="C555" t="s">
+      <c r="D555" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E555" t="s">
         <v>1679</v>
-      </c>
-      <c r="D555" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E555" t="s">
-        <v>1680</v>
       </c>
       <c r="F555" t="s">
         <v>25</v>
@@ -31455,16 +31453,16 @@
         <v>591</v>
       </c>
       <c r="B556" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C556" t="s">
         <v>1681</v>
       </c>
-      <c r="C556" t="s">
+      <c r="D556" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E556" t="s">
         <v>1682</v>
-      </c>
-      <c r="D556" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E556" t="s">
-        <v>1683</v>
       </c>
       <c r="F556" t="s">
         <v>25</v>
@@ -31499,16 +31497,16 @@
         <v>592</v>
       </c>
       <c r="B557" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C557" t="s">
         <v>1684</v>
       </c>
-      <c r="C557" t="s">
+      <c r="D557" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E557" t="s">
         <v>1685</v>
-      </c>
-      <c r="D557" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E557" t="s">
-        <v>1686</v>
       </c>
       <c r="F557" t="s">
         <v>24</v>
@@ -31552,16 +31550,16 @@
         <v>593</v>
       </c>
       <c r="B558" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C558" t="s">
         <v>1687</v>
       </c>
-      <c r="C558" t="s">
+      <c r="D558" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E558" t="s">
         <v>1688</v>
-      </c>
-      <c r="D558" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E558" t="s">
-        <v>1689</v>
       </c>
       <c r="F558" t="s">
         <v>24</v>
@@ -31596,16 +31594,16 @@
         <v>594</v>
       </c>
       <c r="B559" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C559" t="s">
         <v>1690</v>
       </c>
-      <c r="C559" t="s">
+      <c r="D559" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E559" t="s">
         <v>1691</v>
-      </c>
-      <c r="D559" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E559" t="s">
-        <v>1692</v>
       </c>
       <c r="F559" t="s">
         <v>25</v>
@@ -31640,16 +31638,16 @@
         <v>595</v>
       </c>
       <c r="B560" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C560" t="s">
         <v>1693</v>
       </c>
-      <c r="C560" t="s">
+      <c r="D560" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E560" t="s">
         <v>1694</v>
-      </c>
-      <c r="D560" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E560" t="s">
-        <v>1695</v>
       </c>
       <c r="F560" t="s">
         <v>24</v>
@@ -31693,16 +31691,16 @@
         <v>597</v>
       </c>
       <c r="B561" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C561" t="s">
         <v>1696</v>
       </c>
-      <c r="C561" t="s">
+      <c r="D561" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E561" t="s">
         <v>1697</v>
-      </c>
-      <c r="D561" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E561" t="s">
-        <v>1698</v>
       </c>
       <c r="F561" t="s">
         <v>24</v>
@@ -31746,16 +31744,16 @@
         <v>598</v>
       </c>
       <c r="B562" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C562" t="s">
         <v>1699</v>
       </c>
-      <c r="C562" t="s">
+      <c r="D562" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E562" t="s">
         <v>1700</v>
-      </c>
-      <c r="D562" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E562" t="s">
-        <v>1701</v>
       </c>
       <c r="F562" t="s">
         <v>25</v>
@@ -31790,16 +31788,16 @@
         <v>599</v>
       </c>
       <c r="B563" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C563" t="s">
         <v>1702</v>
       </c>
-      <c r="C563" t="s">
+      <c r="D563" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E563" t="s">
         <v>1703</v>
-      </c>
-      <c r="D563" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E563" t="s">
-        <v>1704</v>
       </c>
       <c r="F563" t="s">
         <v>25</v>
@@ -31834,16 +31832,16 @@
         <v>600</v>
       </c>
       <c r="B564" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C564" t="s">
         <v>1705</v>
       </c>
-      <c r="C564" t="s">
+      <c r="D564" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E564" t="s">
         <v>1706</v>
-      </c>
-      <c r="D564" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E564" t="s">
-        <v>1707</v>
       </c>
       <c r="F564" t="s">
         <v>25</v>
@@ -31878,16 +31876,16 @@
         <v>601</v>
       </c>
       <c r="B565" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C565" t="s">
         <v>1708</v>
       </c>
-      <c r="C565" t="s">
+      <c r="D565" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E565" t="s">
         <v>1709</v>
-      </c>
-      <c r="D565" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E565" t="s">
-        <v>1710</v>
       </c>
       <c r="F565" t="s">
         <v>24</v>
@@ -31931,16 +31929,16 @@
         <v>602</v>
       </c>
       <c r="B566" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C566" t="s">
         <v>1711</v>
       </c>
-      <c r="C566" t="s">
+      <c r="D566" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E566" t="s">
         <v>1712</v>
-      </c>
-      <c r="D566" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E566" t="s">
-        <v>1713</v>
       </c>
       <c r="F566" t="s">
         <v>25</v>
@@ -31975,16 +31973,16 @@
         <v>604</v>
       </c>
       <c r="B567" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C567" t="s">
         <v>1714</v>
       </c>
-      <c r="C567" t="s">
+      <c r="D567" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E567" t="s">
         <v>1715</v>
-      </c>
-      <c r="D567" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E567" t="s">
-        <v>1716</v>
       </c>
       <c r="F567" t="s">
         <v>25</v>
@@ -32019,16 +32017,16 @@
         <v>605</v>
       </c>
       <c r="B568" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C568" t="s">
         <v>1717</v>
       </c>
-      <c r="C568" t="s">
+      <c r="D568" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E568" t="s">
         <v>1718</v>
-      </c>
-      <c r="D568" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E568" t="s">
-        <v>1719</v>
       </c>
       <c r="F568" t="s">
         <v>24</v>
@@ -32072,16 +32070,16 @@
         <v>606</v>
       </c>
       <c r="B569" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C569" t="s">
         <v>1720</v>
       </c>
-      <c r="C569" t="s">
+      <c r="D569" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E569" t="s">
         <v>1721</v>
-      </c>
-      <c r="D569" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E569" t="s">
-        <v>1722</v>
       </c>
       <c r="F569" t="s">
         <v>24</v>
@@ -32116,16 +32114,16 @@
         <v>607</v>
       </c>
       <c r="B570" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C570" t="s">
         <v>1723</v>
       </c>
-      <c r="C570" t="s">
+      <c r="D570" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E570" t="s">
         <v>1724</v>
-      </c>
-      <c r="D570" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E570" t="s">
-        <v>1725</v>
       </c>
       <c r="F570" t="s">
         <v>24</v>
@@ -32160,16 +32158,16 @@
         <v>608</v>
       </c>
       <c r="B571" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C571" t="s">
         <v>1726</v>
       </c>
-      <c r="C571" t="s">
+      <c r="D571" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E571" t="s">
         <v>1727</v>
-      </c>
-      <c r="D571" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E571" t="s">
-        <v>1728</v>
       </c>
       <c r="F571" t="s">
         <v>25</v>
@@ -32204,16 +32202,16 @@
         <v>609</v>
       </c>
       <c r="B572" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C572" t="s">
         <v>1729</v>
       </c>
-      <c r="C572" t="s">
+      <c r="D572" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E572" t="s">
         <v>1730</v>
-      </c>
-      <c r="D572" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E572" t="s">
-        <v>1731</v>
       </c>
       <c r="F572" t="s">
         <v>24</v>
@@ -32248,16 +32246,16 @@
         <v>610</v>
       </c>
       <c r="B573" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C573" t="s">
         <v>1732</v>
       </c>
-      <c r="C573" t="s">
+      <c r="D573" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E573" t="s">
         <v>1733</v>
-      </c>
-      <c r="D573" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E573" t="s">
-        <v>1734</v>
       </c>
       <c r="F573" t="s">
         <v>24</v>
@@ -32292,16 +32290,16 @@
         <v>611</v>
       </c>
       <c r="B574" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C574" t="s">
         <v>1735</v>
       </c>
-      <c r="C574" t="s">
+      <c r="D574" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E574" t="s">
         <v>1736</v>
-      </c>
-      <c r="D574" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E574" t="s">
-        <v>1737</v>
       </c>
       <c r="F574" t="s">
         <v>24</v>
@@ -32345,16 +32343,16 @@
         <v>612</v>
       </c>
       <c r="B575" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C575" t="s">
         <v>1738</v>
       </c>
-      <c r="C575" t="s">
-        <v>1739</v>
-      </c>
       <c r="D575" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E575" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="F575" t="s">
         <v>24</v>
@@ -32389,16 +32387,16 @@
         <v>613</v>
       </c>
       <c r="B576" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C576" t="s">
         <v>1740</v>
       </c>
-      <c r="C576" t="s">
+      <c r="D576" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E576" t="s">
         <v>1741</v>
-      </c>
-      <c r="D576" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E576" t="s">
-        <v>1742</v>
       </c>
       <c r="F576" t="s">
         <v>25</v>
@@ -32433,16 +32431,16 @@
         <v>614</v>
       </c>
       <c r="B577" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C577" t="s">
         <v>1743</v>
       </c>
-      <c r="C577" t="s">
+      <c r="D577" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E577" t="s">
         <v>1744</v>
-      </c>
-      <c r="D577" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E577" t="s">
-        <v>1745</v>
       </c>
       <c r="F577" t="s">
         <v>25</v>
@@ -32486,16 +32484,16 @@
         <v>615</v>
       </c>
       <c r="B578" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C578" t="s">
         <v>1746</v>
       </c>
-      <c r="C578" t="s">
+      <c r="D578" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E578" t="s">
         <v>1747</v>
-      </c>
-      <c r="D578" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E578" t="s">
-        <v>1748</v>
       </c>
       <c r="F578" t="s">
         <v>175</v>
@@ -32530,13 +32528,13 @@
         <v>616</v>
       </c>
       <c r="B579" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C579" t="s">
         <v>1749</v>
       </c>
-      <c r="C579" t="s">
-        <v>1750</v>
-      </c>
       <c r="D579" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="F579" t="s">
         <v>175</v>
@@ -32571,16 +32569,16 @@
         <v>617</v>
       </c>
       <c r="B580" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C580" t="s">
         <v>1751</v>
       </c>
-      <c r="C580" t="s">
+      <c r="D580" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E580" t="s">
         <v>1752</v>
-      </c>
-      <c r="D580" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E580" t="s">
-        <v>1753</v>
       </c>
       <c r="F580" t="s">
         <v>25</v>
@@ -32615,16 +32613,16 @@
         <v>618</v>
       </c>
       <c r="B581" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C581" t="s">
         <v>1754</v>
       </c>
-      <c r="C581" t="s">
+      <c r="D581" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E581" t="s">
         <v>1755</v>
-      </c>
-      <c r="D581" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E581" t="s">
-        <v>1756</v>
       </c>
       <c r="F581" t="s">
         <v>25</v>
@@ -32659,13 +32657,13 @@
         <v>619</v>
       </c>
       <c r="B582" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C582" t="s">
         <v>1757</v>
       </c>
-      <c r="C582" t="s">
-        <v>1758</v>
-      </c>
       <c r="D582" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="F582" t="s">
         <v>25</v>
@@ -32700,13 +32698,13 @@
         <v>620</v>
       </c>
       <c r="B583" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C583" t="s">
         <v>1759</v>
       </c>
-      <c r="C583" t="s">
-        <v>1760</v>
-      </c>
       <c r="D583" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="F583" t="s">
         <v>24</v>
@@ -32741,16 +32739,16 @@
         <v>621</v>
       </c>
       <c r="B584" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C584" t="s">
         <v>1761</v>
       </c>
-      <c r="C584" t="s">
+      <c r="D584" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E584" t="s">
         <v>1762</v>
-      </c>
-      <c r="D584" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E584" t="s">
-        <v>1763</v>
       </c>
       <c r="F584" t="s">
         <v>24</v>
@@ -32785,13 +32783,13 @@
         <v>622</v>
       </c>
       <c r="B585" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C585" t="s">
         <v>1764</v>
       </c>
-      <c r="C585" t="s">
-        <v>1765</v>
-      </c>
       <c r="D585" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="F585" t="s">
         <v>24</v>
@@ -32826,16 +32824,16 @@
         <v>623</v>
       </c>
       <c r="B586" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C586" t="s">
         <v>1766</v>
       </c>
-      <c r="C586" t="s">
+      <c r="D586" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E586" t="s">
         <v>1767</v>
-      </c>
-      <c r="D586" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E586" t="s">
-        <v>1768</v>
       </c>
       <c r="F586" t="s">
         <v>25</v>
@@ -32870,16 +32868,16 @@
         <v>624</v>
       </c>
       <c r="B587" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C587" t="s">
         <v>1769</v>
       </c>
-      <c r="C587" t="s">
+      <c r="D587" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E587" t="s">
         <v>1770</v>
-      </c>
-      <c r="D587" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E587" t="s">
-        <v>1771</v>
       </c>
       <c r="F587" t="s">
         <v>25</v>
@@ -32914,16 +32912,16 @@
         <v>625</v>
       </c>
       <c r="B588" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C588" t="s">
         <v>1772</v>
       </c>
-      <c r="C588" t="s">
+      <c r="D588" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E588" t="s">
         <v>1773</v>
-      </c>
-      <c r="D588" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E588" t="s">
-        <v>1774</v>
       </c>
       <c r="F588" t="s">
         <v>25</v>
@@ -32967,13 +32965,13 @@
         <v>626</v>
       </c>
       <c r="B589" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C589" t="s">
         <v>1775</v>
       </c>
-      <c r="C589" t="s">
-        <v>1776</v>
-      </c>
       <c r="D589" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="F589" t="s">
         <v>175</v>
@@ -33008,16 +33006,16 @@
         <v>627</v>
       </c>
       <c r="B590" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C590" t="s">
         <v>1777</v>
       </c>
-      <c r="C590" t="s">
+      <c r="D590" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E590" t="s">
         <v>1778</v>
-      </c>
-      <c r="D590" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E590" t="s">
-        <v>1779</v>
       </c>
       <c r="F590" t="s">
         <v>24</v>
@@ -33061,16 +33059,16 @@
         <v>628</v>
       </c>
       <c r="B591" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C591" t="s">
         <v>1780</v>
       </c>
-      <c r="C591" t="s">
+      <c r="D591" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E591" t="s">
         <v>1781</v>
-      </c>
-      <c r="D591" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E591" t="s">
-        <v>1782</v>
       </c>
       <c r="F591" t="s">
         <v>24</v>
@@ -33114,16 +33112,16 @@
         <v>629</v>
       </c>
       <c r="B592" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C592" t="s">
         <v>1783</v>
       </c>
-      <c r="C592" t="s">
+      <c r="D592" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E592" t="s">
         <v>1784</v>
-      </c>
-      <c r="D592" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E592" t="s">
-        <v>1785</v>
       </c>
       <c r="F592" t="s">
         <v>175</v>
@@ -33158,16 +33156,16 @@
         <v>630</v>
       </c>
       <c r="B593" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C593" t="s">
         <v>1786</v>
       </c>
-      <c r="C593" t="s">
+      <c r="D593" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E593" t="s">
         <v>1787</v>
-      </c>
-      <c r="D593" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E593" t="s">
-        <v>1788</v>
       </c>
       <c r="F593" t="s">
         <v>24</v>
@@ -33211,16 +33209,16 @@
         <v>631</v>
       </c>
       <c r="B594" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C594" t="s">
         <v>1789</v>
       </c>
-      <c r="C594" t="s">
+      <c r="D594" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E594" t="s">
         <v>1790</v>
-      </c>
-      <c r="D594" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E594" t="s">
-        <v>1791</v>
       </c>
       <c r="F594" t="s">
         <v>25</v>
@@ -33255,16 +33253,16 @@
         <v>632</v>
       </c>
       <c r="B595" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C595" t="s">
         <v>1792</v>
       </c>
-      <c r="C595" t="s">
+      <c r="D595" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E595" t="s">
         <v>1793</v>
-      </c>
-      <c r="D595" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E595" t="s">
-        <v>1794</v>
       </c>
       <c r="F595" t="s">
         <v>175</v>
@@ -33299,16 +33297,16 @@
         <v>633</v>
       </c>
       <c r="B596" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C596" t="s">
         <v>1795</v>
       </c>
-      <c r="C596" t="s">
+      <c r="D596" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E596" t="s">
         <v>1796</v>
-      </c>
-      <c r="D596" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E596" t="s">
-        <v>1797</v>
       </c>
       <c r="F596" t="s">
         <v>24</v>
@@ -33361,16 +33359,16 @@
         <v>634</v>
       </c>
       <c r="B597" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C597" t="s">
         <v>1798</v>
       </c>
-      <c r="C597" t="s">
+      <c r="D597" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E597" t="s">
         <v>1799</v>
-      </c>
-      <c r="D597" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E597" t="s">
-        <v>1800</v>
       </c>
       <c r="F597" t="s">
         <v>25</v>
@@ -33414,16 +33412,16 @@
         <v>635</v>
       </c>
       <c r="B598" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C598" t="s">
         <v>1801</v>
       </c>
-      <c r="C598" t="s">
+      <c r="D598" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E598" t="s">
         <v>1802</v>
-      </c>
-      <c r="D598" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E598" t="s">
-        <v>1803</v>
       </c>
       <c r="F598" t="s">
         <v>24</v>
@@ -33458,16 +33456,16 @@
         <v>636</v>
       </c>
       <c r="B599" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C599" t="s">
         <v>1804</v>
       </c>
-      <c r="C599" t="s">
+      <c r="D599" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E599" t="s">
         <v>1805</v>
-      </c>
-      <c r="D599" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E599" t="s">
-        <v>1806</v>
       </c>
       <c r="F599" t="s">
         <v>24</v>
@@ -33502,16 +33500,16 @@
         <v>637</v>
       </c>
       <c r="B600" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C600" t="s">
         <v>1807</v>
       </c>
-      <c r="C600" t="s">
+      <c r="D600" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E600" t="s">
         <v>1808</v>
-      </c>
-      <c r="D600" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E600" t="s">
-        <v>1809</v>
       </c>
       <c r="F600" t="s">
         <v>25</v>
@@ -33546,16 +33544,16 @@
         <v>638</v>
       </c>
       <c r="B601" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C601" t="s">
         <v>1810</v>
       </c>
-      <c r="C601" t="s">
+      <c r="D601" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E601" t="s">
         <v>1811</v>
-      </c>
-      <c r="D601" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E601" t="s">
-        <v>1812</v>
       </c>
       <c r="F601" t="s">
         <v>24</v>
@@ -33590,16 +33588,16 @@
         <v>639</v>
       </c>
       <c r="B602" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C602" t="s">
         <v>1813</v>
       </c>
-      <c r="C602" t="s">
+      <c r="D602" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E602" t="s">
         <v>1814</v>
-      </c>
-      <c r="D602" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E602" t="s">
-        <v>1815</v>
       </c>
       <c r="F602" t="s">
         <v>24</v>
@@ -33634,16 +33632,16 @@
         <v>640</v>
       </c>
       <c r="B603" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C603" t="s">
         <v>1816</v>
       </c>
-      <c r="C603" t="s">
+      <c r="D603" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E603" t="s">
         <v>1817</v>
-      </c>
-      <c r="D603" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E603" t="s">
-        <v>1818</v>
       </c>
       <c r="F603" t="s">
         <v>25</v>
@@ -33678,16 +33676,16 @@
         <v>642</v>
       </c>
       <c r="B604" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C604" t="s">
         <v>1819</v>
       </c>
-      <c r="C604" t="s">
+      <c r="D604" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E604" t="s">
         <v>1820</v>
-      </c>
-      <c r="D604" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E604" t="s">
-        <v>1821</v>
       </c>
       <c r="F604" t="s">
         <v>24</v>
@@ -33722,13 +33720,13 @@
         <v>643</v>
       </c>
       <c r="B605" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C605" t="s">
         <v>1822</v>
       </c>
-      <c r="C605" t="s">
-        <v>1823</v>
-      </c>
       <c r="D605" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="F605" t="s">
         <v>25</v>
@@ -33763,16 +33761,16 @@
         <v>644</v>
       </c>
       <c r="B606" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C606" t="s">
         <v>1824</v>
       </c>
-      <c r="C606" t="s">
+      <c r="D606" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E606" t="s">
         <v>1825</v>
-      </c>
-      <c r="D606" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E606" t="s">
-        <v>1826</v>
       </c>
       <c r="F606" t="s">
         <v>32</v>
@@ -33816,16 +33814,16 @@
         <v>645</v>
       </c>
       <c r="B607" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C607" t="s">
         <v>1827</v>
       </c>
-      <c r="C607" t="s">
+      <c r="D607" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E607" t="s">
         <v>1828</v>
-      </c>
-      <c r="D607" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E607" t="s">
-        <v>1829</v>
       </c>
       <c r="F607" t="s">
         <v>25</v>
@@ -33860,16 +33858,16 @@
         <v>646</v>
       </c>
       <c r="B608" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C608" t="s">
         <v>1830</v>
       </c>
-      <c r="C608" t="s">
+      <c r="D608" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E608" t="s">
         <v>1831</v>
-      </c>
-      <c r="D608" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E608" t="s">
-        <v>1832</v>
       </c>
       <c r="F608" t="s">
         <v>25</v>
@@ -33913,16 +33911,16 @@
         <v>647</v>
       </c>
       <c r="B609" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C609" t="s">
         <v>1833</v>
       </c>
-      <c r="C609" t="s">
+      <c r="D609" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E609" t="s">
         <v>1834</v>
-      </c>
-      <c r="D609" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E609" t="s">
-        <v>1835</v>
       </c>
       <c r="F609" t="s">
         <v>25</v>
@@ -33957,16 +33955,16 @@
         <v>648</v>
       </c>
       <c r="B610" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C610" t="s">
         <v>1836</v>
       </c>
-      <c r="C610" t="s">
+      <c r="D610" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E610" t="s">
         <v>1837</v>
-      </c>
-      <c r="D610" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E610" t="s">
-        <v>1838</v>
       </c>
       <c r="F610" t="s">
         <v>175</v>
@@ -34001,13 +33999,13 @@
         <v>649</v>
       </c>
       <c r="B611" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C611" t="s">
         <v>1839</v>
       </c>
-      <c r="C611" t="s">
-        <v>1840</v>
-      </c>
       <c r="D611" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="F611" t="s">
         <v>25</v>
@@ -34051,13 +34049,13 @@
         <v>651</v>
       </c>
       <c r="B612" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C612" t="s">
         <v>1841</v>
       </c>
-      <c r="C612" t="s">
-        <v>1842</v>
-      </c>
       <c r="D612" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="F612" t="s">
         <v>24</v>
@@ -34092,13 +34090,13 @@
         <v>652</v>
       </c>
       <c r="B613" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C613" t="s">
         <v>1843</v>
       </c>
-      <c r="C613" t="s">
-        <v>1844</v>
-      </c>
       <c r="D613" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="F613" t="s">
         <v>24</v>
@@ -34133,16 +34131,16 @@
         <v>653</v>
       </c>
       <c r="B614" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C614" t="s">
         <v>1845</v>
       </c>
-      <c r="C614" t="s">
+      <c r="D614" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E614" t="s">
         <v>1846</v>
-      </c>
-      <c r="D614" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E614" t="s">
-        <v>1847</v>
       </c>
       <c r="F614" t="s">
         <v>24</v>
@@ -34177,16 +34175,16 @@
         <v>654</v>
       </c>
       <c r="B615" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C615" t="s">
         <v>1848</v>
       </c>
-      <c r="C615" t="s">
+      <c r="D615" t="s">
         <v>1849</v>
       </c>
-      <c r="D615" t="s">
+      <c r="E615" t="s">
         <v>1850</v>
-      </c>
-      <c r="E615" t="s">
-        <v>1851</v>
       </c>
       <c r="F615" t="s">
         <v>25</v>
@@ -34221,16 +34219,16 @@
         <v>655</v>
       </c>
       <c r="B616" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C616" t="s">
         <v>1852</v>
       </c>
-      <c r="C616" t="s">
+      <c r="D616" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E616" t="s">
         <v>1853</v>
-      </c>
-      <c r="D616" t="s">
-        <v>1850</v>
-      </c>
-      <c r="E616" t="s">
-        <v>1854</v>
       </c>
       <c r="F616" t="s">
         <v>25</v>
@@ -34265,16 +34263,16 @@
         <v>656</v>
       </c>
       <c r="B617" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C617" t="s">
         <v>1855</v>
       </c>
-      <c r="C617" t="s">
+      <c r="D617" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E617" t="s">
         <v>1856</v>
-      </c>
-      <c r="D617" t="s">
-        <v>1850</v>
-      </c>
-      <c r="E617" t="s">
-        <v>1857</v>
       </c>
       <c r="F617" t="s">
         <v>25</v>
@@ -34309,16 +34307,16 @@
         <v>657</v>
       </c>
       <c r="B618" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C618" t="s">
         <v>1858</v>
       </c>
-      <c r="C618" t="s">
+      <c r="D618" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E618" t="s">
         <v>1859</v>
-      </c>
-      <c r="D618" t="s">
-        <v>1850</v>
-      </c>
-      <c r="E618" t="s">
-        <v>1860</v>
       </c>
       <c r="F618" t="s">
         <v>57</v>
@@ -34353,16 +34351,16 @@
         <v>658</v>
       </c>
       <c r="B619" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C619" t="s">
         <v>1861</v>
       </c>
-      <c r="C619" t="s">
+      <c r="D619" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E619" t="s">
         <v>1862</v>
-      </c>
-      <c r="D619" t="s">
-        <v>1850</v>
-      </c>
-      <c r="E619" t="s">
-        <v>1863</v>
       </c>
       <c r="F619" t="s">
         <v>25</v>
@@ -34385,16 +34383,16 @@
         <v>659</v>
       </c>
       <c r="B620" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C620" t="s">
         <v>1864</v>
       </c>
-      <c r="C620" t="s">
+      <c r="D620" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E620" t="s">
         <v>1865</v>
-      </c>
-      <c r="D620" t="s">
-        <v>1850</v>
-      </c>
-      <c r="E620" t="s">
-        <v>1866</v>
       </c>
       <c r="F620" t="s">
         <v>25</v>
@@ -34417,16 +34415,16 @@
         <v>660</v>
       </c>
       <c r="B621" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C621" t="s">
         <v>1867</v>
       </c>
-      <c r="C621" t="s">
+      <c r="D621" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E621" t="s">
         <v>1868</v>
-      </c>
-      <c r="D621" t="s">
-        <v>1850</v>
-      </c>
-      <c r="E621" t="s">
-        <v>1869</v>
       </c>
       <c r="F621" t="s">
         <v>25</v>
@@ -34449,16 +34447,16 @@
         <v>661</v>
       </c>
       <c r="B622" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C622" t="s">
         <v>1870</v>
       </c>
-      <c r="C622" t="s">
+      <c r="D622" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E622" t="s">
         <v>1871</v>
-      </c>
-      <c r="D622" t="s">
-        <v>1850</v>
-      </c>
-      <c r="E622" t="s">
-        <v>1872</v>
       </c>
       <c r="F622" t="s">
         <v>25</v>
@@ -34493,16 +34491,16 @@
         <v>662</v>
       </c>
       <c r="B623" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C623" t="s">
         <v>1873</v>
       </c>
-      <c r="C623" t="s">
+      <c r="D623" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E623" t="s">
         <v>1874</v>
-      </c>
-      <c r="D623" t="s">
-        <v>1850</v>
-      </c>
-      <c r="E623" t="s">
-        <v>1875</v>
       </c>
       <c r="F623" t="s">
         <v>25</v>
@@ -34537,16 +34535,16 @@
         <v>663</v>
       </c>
       <c r="B624" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C624" t="s">
         <v>1876</v>
       </c>
-      <c r="C624" t="s">
+      <c r="D624" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E624" t="s">
         <v>1877</v>
-      </c>
-      <c r="D624" t="s">
-        <v>1850</v>
-      </c>
-      <c r="E624" t="s">
-        <v>1878</v>
       </c>
       <c r="F624" t="s">
         <v>57</v>
@@ -34581,16 +34579,16 @@
         <v>664</v>
       </c>
       <c r="B625" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C625" t="s">
         <v>1879</v>
       </c>
-      <c r="C625" t="s">
+      <c r="D625" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E625" t="s">
         <v>1880</v>
-      </c>
-      <c r="D625" t="s">
-        <v>1850</v>
-      </c>
-      <c r="E625" t="s">
-        <v>1881</v>
       </c>
       <c r="F625" t="s">
         <v>25</v>
@@ -34613,13 +34611,13 @@
         <v>665</v>
       </c>
       <c r="B626" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C626" t="s">
         <v>1882</v>
       </c>
-      <c r="C626" t="s">
-        <v>1883</v>
-      </c>
       <c r="D626" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="F626" t="s">
         <v>57</v>
